--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_image_text_ratio.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_image_text_ratio.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C2" t="n">
-        <v>53.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
